--- a/excel/库存健康度与补货调拨建议表.xlsx
+++ b/excel/库存健康度与补货调拨建议表.xlsx
@@ -27,7 +27,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -79,8 +79,13 @@
       <color rgb="00548235"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="微软雅黑"/>
+      <color rgb="00C00000"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -122,6 +127,16 @@
         <fgColor rgb="00D9D9D9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCE4E4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9E2F3"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -149,7 +164,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -205,6 +220,19 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -660,7 +688,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>核心结论（5 条）</t>
+          <t>核心结论（6 条）</t>
         </is>
       </c>
       <c r="B8" s="2" t="n"/>
@@ -697,6 +725,13 @@
       <c r="A13" s="4" t="inlineStr">
         <is>
           <t>⑤ 数据质量侧发现 9 条「负库存」记录（销量 &gt; 期初 + 入库），分布在 7 月 1 条、8 月 3 条、9 月 5 条，集中在 5 个「门店 × 商品」组合上，其中 4 条的次月期初库存被系统回补至 15 件底线 —— 这 9 条不是脏数据，而是断货超卖的业务证据，恰好出现在需求最高的款上。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>⑥ 结论落到行动：门店级补货需求 715 件 → 跨店调拨解决 145 件（¥120,355，零采购成本）→ 实际需采购 530 件（¥131,470）。「先调拨、后采购」的优先级由此量化确定。</t>
         </is>
       </c>
     </row>
@@ -3808,9 +3843,9 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="21" t="inlineStr">
-        <is>
-          <t>若全部走采购补货：共 715 件，按售价计约 ¥260,485</t>
+      <c r="A17" s="26" t="inlineStr">
+        <is>
+          <t>门店级补货需求合计 715 件（按售价计约 ¥260,485）。注意：这不是采购量 —— 其中 145 件可由跨店调拨解决，实际需采购 530 件 / 约 ¥131,470（见「全网供需缺口」表）。</t>
         </is>
       </c>
     </row>
@@ -4022,7 +4057,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4033,6 +4068,7 @@
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -4097,6 +4133,11 @@
           <t>全网周转天数</t>
         </is>
       </c>
+      <c r="I3" s="8" t="inlineStr">
+        <is>
+          <t>全网缺口</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="9" t="inlineStr">
@@ -4129,6 +4170,9 @@
       <c r="H4" s="23" t="n">
         <v>-4.4</v>
       </c>
+      <c r="I4" s="27" t="n">
+        <v>225</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
@@ -4161,6 +4205,9 @@
       <c r="H5" s="23" t="n">
         <v>-1.3</v>
       </c>
+      <c r="I5" s="27" t="n">
+        <v>195</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
@@ -4193,6 +4240,9 @@
       <c r="H6" s="24" t="n">
         <v>17.4</v>
       </c>
+      <c r="I6" s="27" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
@@ -4225,6 +4275,9 @@
       <c r="H7" s="24" t="n">
         <v>19.1</v>
       </c>
+      <c r="I7" s="27" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
@@ -4257,6 +4310,9 @@
       <c r="H8" s="24" t="n">
         <v>33.9</v>
       </c>
+      <c r="I8" s="9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
@@ -4289,6 +4345,9 @@
       <c r="H9" s="12" t="n">
         <v>46.4</v>
       </c>
+      <c r="I9" s="9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
@@ -4321,6 +4380,9 @@
       <c r="H10" s="12" t="n">
         <v>46.4</v>
       </c>
+      <c r="I10" s="9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
@@ -4353,6 +4415,9 @@
       <c r="H11" s="12" t="n">
         <v>51.6</v>
       </c>
+      <c r="I11" s="9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
@@ -4385,6 +4450,9 @@
       <c r="H12" s="12" t="n">
         <v>59.3</v>
       </c>
+      <c r="I12" s="9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
@@ -4417,6 +4485,9 @@
       <c r="H13" s="12" t="n">
         <v>60</v>
       </c>
+      <c r="I13" s="9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
@@ -4449,6 +4520,9 @@
       <c r="H14" s="12" t="n">
         <v>62.9</v>
       </c>
+      <c r="I14" s="9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
@@ -4481,6 +4555,9 @@
       <c r="H15" s="12" t="n">
         <v>66.7</v>
       </c>
+      <c r="I15" s="9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
@@ -4513,6 +4590,9 @@
       <c r="H16" s="12" t="n">
         <v>83.2</v>
       </c>
+      <c r="I16" s="9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="9" t="inlineStr">
@@ -4545,6 +4625,9 @@
       <c r="H17" s="12" t="n">
         <v>112.8</v>
       </c>
+      <c r="I17" s="9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
@@ -4576,6 +4659,40 @@
       </c>
       <c r="H18" s="12" t="n">
         <v>126.4</v>
+      </c>
+      <c r="I18" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="28" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
+      </c>
+      <c r="B19" s="29" t="n"/>
+      <c r="C19" s="29" t="n"/>
+      <c r="D19" s="29" t="n"/>
+      <c r="E19" s="29" t="n"/>
+      <c r="F19" s="29" t="n"/>
+      <c r="G19" s="29" t="n"/>
+      <c r="H19" s="29" t="n"/>
+      <c r="I19" s="30" t="n">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="26" t="inlineStr">
+        <is>
+          <t>全网缺口合计 530 件，按售价计约 ¥131,470（P002 225 / P007 195 / P001 55 / P008 55）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>注意口径：这是「采购量」，不是「补货需求 715 件」。715 含可由跨店调拨解决的 145 件，以及 P009 那 40 件（全网有货，只是富余店仅「偏高」档、未达 90 天调拨阈值）。</t>
+        </is>
       </c>
     </row>
   </sheetData>
